--- a/basedatos_partidas/salida/descompuestos/CT-06-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-06-010.xlsx
@@ -539,10 +539,10 @@
         <v>12.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="H10" t="n">
-        <v>13.23</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="H11" t="n">
-        <v>3.12</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>4.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H12" t="n">
-        <v>6.48</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="13">
@@ -643,10 +643,10 @@
         <v>0.022</v>
       </c>
       <c r="G14" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="15">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>27.83</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="17">
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>36.5</v>
+        <v>32.34</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>36.86</v>
+        <v>32.66</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-06-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H28"/>
+  <dimension ref="A3:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-MORT-EST</t>
+          <t>MT-CEMENTO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -558,348 +558,400 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Mortero de pega de resistencia controlada para mampostería estructural.</t>
+          <t>Cemento Portland gris tipo I, en saco. Para mortero de pega de resistencia controlada.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>5.85</v>
       </c>
       <c r="G11" t="n">
-        <v>0.15</v>
+        <v>0.225</v>
       </c>
       <c r="H11" t="n">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-ACERO-CAB</t>
+          <t>MT-ARENA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Acero de refuerzo en cabillas corrugadas, límite elástico 4.200 kg/cm2, cortado y doblado.</t>
+          <t>Arena lavada de río, puesta en obra, para camas de asiento y rellenos de zanja. Para mortero de pega de resistencia controlada.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.8</v>
+        <v>0.013</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2</v>
+        <v>22</v>
       </c>
       <c r="H12" t="n">
-        <v>5.76</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT-ESCALERILLA</t>
+          <t>MT-AGUA-OBRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Escalerilla o junta de refuerzo horizontal para mampostería.</t>
+          <t>Agua para amasado, humectación de rellenos y compactación. Para mortero de pega de resistencia controlada.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>0.00286</v>
       </c>
       <c r="G13" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MT-GROUT-CELDA</t>
+          <t>MT-ACERO-CAB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Concreto fluido de relleno de celdas para mampostería estructural.</t>
+          <t>Acero de refuerzo en cabillas corrugadas, límite elástico 4.200 kg/cm2, cortado y doblado.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.022</v>
+        <v>4.8</v>
       </c>
       <c r="G14" t="n">
-        <v>126</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.77</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>MT-ESCALERILLA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Escalerilla o junta de refuerzo horizontal para mampostería.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MT-GROUT-CELDA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Concreto fluido de relleno de celdas para mampostería estructural.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G16" t="n">
+        <v>126</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>MT-ALAMBRE</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Alambre recocido para amarre de acero de refuerzo.</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F17" t="n">
         <v>0.08</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G17" t="n">
         <v>1.9</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="16">
-      <c r="F16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Subtotal materiales:</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>23.67</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="H18" t="n">
+        <v>23.33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>MQ-MEZCL</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Mezcladora de concreto y mortero de 1 saco, incluida amortización y combustible.</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
         <v>0.09</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" t="n">
         <v>3.6</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H20" t="n">
         <v>0.32</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>MQ-VIBRADOR</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Vibrador de aguja con motor, para compactación de concreto.</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>0.06</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G21" t="n">
         <v>3.4</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="F20" s="1" t="inlineStr">
+    <row r="22">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Subtotal equipo y maquinaria:</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H22" t="n">
         <v>0.52</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="23">
+      <c r="A23" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Mano de obra</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MO-OF1-ALB</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Oficial de 1ª albañil.</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MO-OF1-CAB</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Oficial de 1ª cabillero (armador de acero de refuerzo).</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>MO-OF1-ALB</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Oficial de 1ª albañil.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MO-OF1-CAB</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Oficial de 1ª cabillero (armador de acero de refuerzo).</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>MO-AYU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Ayudante.</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>0.82</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>3.5</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>2.87</v>
       </c>
     </row>
-    <row r="25">
-      <c r="F25" s="1" t="inlineStr">
+    <row r="27">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Subtotal mano de obra:</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>8.15</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="28">
+      <c r="A28" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="D27" t="inlineStr">
+    <row r="29">
+      <c r="D29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G27" t="n">
-        <v>32.34</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="G29" t="n">
+        <v>32</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.32</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="5" t="n">
-        <v>32.66</v>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="5" t="n">
+        <v>32.32</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-06-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 06 Paredes y tabiquería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Mampostería estructural</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
